--- a/data/videos_canal_youtube.xlsx
+++ b/data/videos_canal_youtube.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11 02:44</t>
+          <t>2026-08-11 03:00</t>
         </is>
       </c>
     </row>

--- a/data/videos_canal_youtube.xlsx
+++ b/data/videos_canal_youtube.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11 03:00</t>
+          <t>2026-08-11 03:16</t>
         </is>
       </c>
     </row>

--- a/data/videos_canal_youtube.xlsx
+++ b/data/videos_canal_youtube.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11 03:16</t>
+          <t>2026-08-11 09:37</t>
         </is>
       </c>
     </row>

--- a/data/videos_canal_youtube.xlsx
+++ b/data/videos_canal_youtube.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11 09:37</t>
+          <t>2026-08-11 09:44</t>
         </is>
       </c>
     </row>

--- a/data/videos_canal_youtube.xlsx
+++ b/data/videos_canal_youtube.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11 09:44</t>
+          <t>2026-08-11 12:11</t>
         </is>
       </c>
     </row>
